--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -499,7 +499,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v/>
+        <v>250040698327080@lid</v>
       </c>
       <c r="B8">
         <v>919867623441</v>
